--- a/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>618505</t>
+          <t>614604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>682290</t>
+          <t>676515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>966529</t>
+          <t>963631</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1028598</t>
+          <t>1025056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1601758</t>
+          <t>1601808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1692406</t>
+          <t>1691276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>349433</t>
+          <t>355208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413218</t>
+          <t>417119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286515</t>
+          <t>290057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348584</t>
+          <t>351482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>654429</t>
+          <t>655559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745077</t>
+          <t>745027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>562139</t>
+          <t>560680</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>644454</t>
+          <t>639006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>762825</t>
+          <t>763045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>840127</t>
+          <t>843641</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1335469</t>
+          <t>1344811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1453407</t>
+          <t>1455783</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1048959</t>
+          <t>1054407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1131274</t>
+          <t>1132733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>747546</t>
+          <t>744032</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>824848</t>
+          <t>824628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1827679</t>
+          <t>1825303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1945617</t>
+          <t>1936275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>184355</t>
+          <t>183309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>230200</t>
+          <t>231634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>216502</t>
+          <t>218972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261768</t>
+          <t>261814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>413948</t>
+          <t>414535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>481628</t>
+          <t>478275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>321208</t>
+          <t>319774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>367053</t>
+          <t>368099</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>214644</t>
+          <t>214598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259910</t>
+          <t>257440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>546192</t>
+          <t>549545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613872</t>
+          <t>613285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1395018</t>
+          <t>1395138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1518207</t>
+          <t>1511228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1984896</t>
+          <t>1987034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2100982</t>
+          <t>2098254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3412677</t>
+          <t>3411780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3580049</t>
+          <t>3578155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1758336</t>
+          <t>1765315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1881525</t>
+          <t>1881405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1278215</t>
+          <t>1280943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1394301</t>
+          <t>1392163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3075692</t>
+          <t>3077586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3243064</t>
+          <t>3243961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>704918</t>
+          <t>707371</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>761630</t>
+          <t>761539</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1118826</t>
+          <t>1118731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1170695</t>
+          <t>1172441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1843273</t>
+          <t>1844269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1918691</t>
+          <t>1919074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>213013</t>
+          <t>213104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269725</t>
+          <t>267272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167102</t>
+          <t>165356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>218971</t>
+          <t>219066</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>393749</t>
+          <t>393366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>469167</t>
+          <t>468171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>846920</t>
+          <t>840404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>934917</t>
+          <t>933256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>972088</t>
+          <t>974095</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1057069</t>
+          <t>1058863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1838830</t>
+          <t>1846315</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1963113</t>
+          <t>1962254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1029040</t>
+          <t>1030701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1117037</t>
+          <t>1123553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>700734</t>
+          <t>698940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>785715</t>
+          <t>783708</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1758647</t>
+          <t>1759506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1882930</t>
+          <t>1875445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>196195</t>
+          <t>193918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>243438</t>
+          <t>242613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>216246</t>
+          <t>216822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260526</t>
+          <t>261272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>424413</t>
+          <t>426572</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>489958</t>
+          <t>488743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237743</t>
+          <t>238568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284986</t>
+          <t>287263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198105</t>
+          <t>197359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>242385</t>
+          <t>241809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>449855</t>
+          <t>451070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>515400</t>
+          <t>513241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,61%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1778158</t>
+          <t>1786726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1895592</t>
+          <t>1904001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2339685</t>
+          <t>2343503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2453726</t>
+          <t>2455327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4155919</t>
+          <t>4159327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4327726</t>
+          <t>4319456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,94%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1524190</t>
+          <t>1515781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1641624</t>
+          <t>1633056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1100504</t>
+          <t>1098903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1214545</t>
+          <t>1210727</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2646286</t>
+          <t>2654556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2818093</t>
+          <t>2814685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>497071</t>
+          <t>496596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>546601</t>
+          <t>546789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>811824</t>
+          <t>810372</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>856990</t>
+          <t>858259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1323912</t>
+          <t>1323351</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1394322</t>
+          <t>1395906</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>207746</t>
+          <t>207558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257276</t>
+          <t>257751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137670</t>
+          <t>136401</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182836</t>
+          <t>184288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>354685</t>
+          <t>353101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425095</t>
+          <t>425656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>901657</t>
+          <t>897028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>989034</t>
+          <t>990808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1031359</t>
+          <t>1029205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1120392</t>
+          <t>1121418</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1955855</t>
+          <t>1952708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2083115</t>
+          <t>2085194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1087351</t>
+          <t>1085577</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1174728</t>
+          <t>1179357</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>867908</t>
+          <t>866882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>956941</t>
+          <t>959095</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1981570</t>
+          <t>1979491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2108830</t>
+          <t>2111977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188873</t>
+          <t>190909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>235969</t>
+          <t>239126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>230976</t>
+          <t>232488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>279840</t>
+          <t>281243</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>437872</t>
+          <t>437860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>503417</t>
+          <t>504420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310917</t>
+          <t>307760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>358013</t>
+          <t>355977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>269300</t>
+          <t>267897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318164</t>
+          <t>316652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592610</t>
+          <t>591607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658155</t>
+          <t>658167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1625187</t>
+          <t>1621770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1738202</t>
+          <t>1739547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2107943</t>
+          <t>2110727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2226847</t>
+          <t>2230096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3762017</t>
+          <t>3773653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3933488</t>
+          <t>3936288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1639416</t>
+          <t>1638071</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1752431</t>
+          <t>1755848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1305253</t>
+          <t>1302004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1424157</t>
+          <t>1421373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2976230</t>
+          <t>2973430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3147701</t>
+          <t>3136065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>255418</t>
+          <t>256446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299445</t>
+          <t>300257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>461850</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>501213</t>
+          <t>501759</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>732546</t>
+          <t>731421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>791548</t>
+          <t>789749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215493</t>
+          <t>214681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>259520</t>
+          <t>258492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254295</t>
+          <t>253749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293658</t>
+          <t>294638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>478898</t>
+          <t>480697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537900</t>
+          <t>539025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>454661</t>
+          <t>446681</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>742277</t>
+          <t>736898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>723050</t>
+          <t>722027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1267091</t>
+          <t>1211469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1315341</t>
+          <t>1290098</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1970595</t>
+          <t>1968378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1548050</t>
+          <t>1553429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1835666</t>
+          <t>1843646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>970732</t>
+          <t>1026354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1514773</t>
+          <t>1515796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2557555</t>
+          <t>2559772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3212809</t>
+          <t>3238052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158163</t>
+          <t>158727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207765</t>
+          <t>208603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176424</t>
+          <t>179386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>219385</t>
+          <t>221097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>349655</t>
+          <t>350541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>411754</t>
+          <t>415282</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>438858</t>
+          <t>438020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>488460</t>
+          <t>487896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441078</t>
+          <t>439366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>484039</t>
+          <t>481077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>895332</t>
+          <t>891804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>957431</t>
+          <t>956545</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>842040</t>
+          <t>874697</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1215615</t>
+          <t>1210115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1406286</t>
+          <t>1408107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1946674</t>
+          <t>1964442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2404899</t>
+          <t>2411425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3080944</t>
+          <t>3046895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2236274</t>
+          <t>2241774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2609849</t>
+          <t>2577192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1707120</t>
+          <t>1689352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2247508</t>
+          <t>2245687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4024739</t>
+          <t>4058788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4700784</t>
+          <t>4694258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>614604</t>
+          <t>614546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>676515</t>
+          <t>678009</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>963631</t>
+          <t>965566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1025056</t>
+          <t>1027390</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1601808</t>
+          <t>1600211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1691276</t>
+          <t>1691984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355208</t>
+          <t>353714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417119</t>
+          <t>417177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290057</t>
+          <t>287723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>351482</t>
+          <t>349547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>655559</t>
+          <t>654851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745027</t>
+          <t>746624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>560680</t>
+          <t>563378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>639006</t>
+          <t>642493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>763045</t>
+          <t>759604</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>843641</t>
+          <t>842094</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1344811</t>
+          <t>1339130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1455783</t>
+          <t>1458441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1054407</t>
+          <t>1050920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1132733</t>
+          <t>1130035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>744032</t>
+          <t>745579</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>824628</t>
+          <t>828069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1825303</t>
+          <t>1822645</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1936275</t>
+          <t>1941956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>183309</t>
+          <t>183833</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>231634</t>
+          <t>230094</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>218972</t>
+          <t>215387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261814</t>
+          <t>260637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>414535</t>
+          <t>413610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>478275</t>
+          <t>479320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319774</t>
+          <t>321314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>368099</t>
+          <t>367575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>214598</t>
+          <t>215775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257440</t>
+          <t>261025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>549545</t>
+          <t>548500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613285</t>
+          <t>614210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1395138</t>
+          <t>1400719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1511228</t>
+          <t>1511926</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1987034</t>
+          <t>1983020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2098254</t>
+          <t>2093417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3411780</t>
+          <t>3414949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3578155</t>
+          <t>3578136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1765315</t>
+          <t>1764617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1881405</t>
+          <t>1875824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1280943</t>
+          <t>1285780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1392163</t>
+          <t>1396177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3077586</t>
+          <t>3077605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3243961</t>
+          <t>3240792</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>707371</t>
+          <t>709581</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>761539</t>
+          <t>761744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1118731</t>
+          <t>1119187</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1172441</t>
+          <t>1171165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1844269</t>
+          <t>1842590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1919074</t>
+          <t>1921346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>213104</t>
+          <t>212899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267272</t>
+          <t>265062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165356</t>
+          <t>166632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219066</t>
+          <t>218610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>393366</t>
+          <t>391094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>468171</t>
+          <t>469850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>840404</t>
+          <t>843688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>933256</t>
+          <t>932945</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>974095</t>
+          <t>973732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1058863</t>
+          <t>1060167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1846315</t>
+          <t>1839324</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1962254</t>
+          <t>1959956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1030701</t>
+          <t>1031012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1123553</t>
+          <t>1120269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>698940</t>
+          <t>697636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>783708</t>
+          <t>784071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1759506</t>
+          <t>1761804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1875445</t>
+          <t>1882436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>193918</t>
+          <t>196821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242613</t>
+          <t>244229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>216822</t>
+          <t>213450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261272</t>
+          <t>259939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>426572</t>
+          <t>428533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>488743</t>
+          <t>491030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238568</t>
+          <t>236952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287263</t>
+          <t>284360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197359</t>
+          <t>198692</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241809</t>
+          <t>245181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>451070</t>
+          <t>448783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>513241</t>
+          <t>511280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1786726</t>
+          <t>1779835</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1904001</t>
+          <t>1900380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2343503</t>
+          <t>2342277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2455327</t>
+          <t>2459816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4159327</t>
+          <t>4151724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4319456</t>
+          <t>4324876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1515781</t>
+          <t>1519402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1633056</t>
+          <t>1639947</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1098903</t>
+          <t>1094414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1210727</t>
+          <t>1211953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2654556</t>
+          <t>2649136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2814685</t>
+          <t>2822288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>496596</t>
+          <t>497320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>546789</t>
+          <t>548893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>810372</t>
+          <t>813142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>858259</t>
+          <t>858815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1323351</t>
+          <t>1322971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1395906</t>
+          <t>1392424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>207558</t>
+          <t>205454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257751</t>
+          <t>257027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136401</t>
+          <t>135845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184288</t>
+          <t>181518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>353101</t>
+          <t>356583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425656</t>
+          <t>426036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>897028</t>
+          <t>901156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>990808</t>
+          <t>993141</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1029205</t>
+          <t>1030371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1121418</t>
+          <t>1122327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1952708</t>
+          <t>1952432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2085194</t>
+          <t>2082563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1085577</t>
+          <t>1083244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1179357</t>
+          <t>1175229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>866882</t>
+          <t>865973</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959095</t>
+          <t>957929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1979491</t>
+          <t>1982122</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2111977</t>
+          <t>2112253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,97%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>190909</t>
+          <t>190455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>239126</t>
+          <t>236334</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>232488</t>
+          <t>233438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>281243</t>
+          <t>280837</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>437860</t>
+          <t>436654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>504420</t>
+          <t>508547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307760</t>
+          <t>310552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>355977</t>
+          <t>356431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267897</t>
+          <t>268303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316652</t>
+          <t>315702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>591607</t>
+          <t>587480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658167</t>
+          <t>659373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,16%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1621770</t>
+          <t>1621533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1739547</t>
+          <t>1738844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2110727</t>
+          <t>2110791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2230096</t>
+          <t>2232839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3773653</t>
+          <t>3767552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3936288</t>
+          <t>3930684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,89%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1638071</t>
+          <t>1638774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1755848</t>
+          <t>1756085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1302004</t>
+          <t>1299261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1421373</t>
+          <t>1421309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2973430</t>
+          <t>2979034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3136065</t>
+          <t>3142166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>276915</t>
+          <t>291268</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>256446</t>
+          <t>267601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>300257</t>
+          <t>315611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>482580</t>
+          <t>517509</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>494684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>501759</t>
+          <t>538462</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>759495</t>
+          <t>808777</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>731421</t>
+          <t>779241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>789749</t>
+          <t>844961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>238023</t>
+          <t>287261</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214681</t>
+          <t>262918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>258492</t>
+          <t>310928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>272928</t>
+          <t>304529</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253749</t>
+          <t>283576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294638</t>
+          <t>327354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>510951</t>
+          <t>591790</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>480697</t>
+          <t>555606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539025</t>
+          <t>621326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>645229</t>
+          <t>675345</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>446681</t>
+          <t>632015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>736898</t>
+          <t>726744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>880361</t>
+          <t>743212</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>722027</t>
+          <t>701728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1211469</t>
+          <t>785754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1525590</t>
+          <t>1418558</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1290098</t>
+          <t>1354808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1968378</t>
+          <t>1480076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1645098</t>
+          <t>1555221</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1553429</t>
+          <t>1503822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1843646</t>
+          <t>1598551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1357462</t>
+          <t>1428180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1026354</t>
+          <t>1385638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1515796</t>
+          <t>1469664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3002560</t>
+          <t>2983401</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2559772</t>
+          <t>2921883</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3238052</t>
+          <t>3047151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>181938</t>
+          <t>194718</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158727</t>
+          <t>170272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>208603</t>
+          <t>221123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>199190</t>
+          <t>220042</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179386</t>
+          <t>197801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221097</t>
+          <t>240937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>381128</t>
+          <t>414760</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>350541</t>
+          <t>377706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>415282</t>
+          <t>446306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>464685</t>
+          <t>516869</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>438020</t>
+          <t>490464</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487896</t>
+          <t>541315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>461273</t>
+          <t>514835</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>439366</t>
+          <t>493940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>481077</t>
+          <t>537076</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>925958</t>
+          <t>1031704</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>891804</t>
+          <t>1000158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>956545</t>
+          <t>1068758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,89%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1104081</t>
+          <t>1161332</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>874697</t>
+          <t>1099569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1210115</t>
+          <t>1219351</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1562131</t>
+          <t>1480763</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1408107</t>
+          <t>1428908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1964442</t>
+          <t>1533032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2666213</t>
+          <t>2642096</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2411425</t>
+          <t>2560371</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3046895</t>
+          <t>2720350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2347808</t>
+          <t>2359351</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2241774</t>
+          <t>2301332</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2577192</t>
+          <t>2421114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2091663</t>
+          <t>2247544</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1689352</t>
+          <t>2195275</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2245687</t>
+          <t>2299399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4439470</t>
+          <t>4606894</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4058788</t>
+          <t>4528640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4694258</t>
+          <t>4688619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>64,68%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
